--- a/FoodBank Files/Product In.xlsx
+++ b/FoodBank Files/Product In.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/860d755c183b4dc3/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icarusjay\Downloads\xampp\htdocs\FoodBank Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5744E919-12B7-481C-ADF2-EAB54B77F77F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D120A4DC-8713-44D5-9F08-8DF8273EF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FEF8D386-D128-4069-BDCD-FE457B1D9085}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{FEF8D386-D128-4069-BDCD-FE457B1D9085}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="197">
   <si>
     <t>ENTRY DATE</t>
   </si>
@@ -137,9 +137,6 @@
     <t>Coke Vanilla</t>
   </si>
   <si>
-    <t>2025-08-07</t>
-  </si>
-  <si>
     <t>Sprite Lemon</t>
   </si>
   <si>
@@ -149,21 +146,12 @@
     <t>Sprite Zero</t>
   </si>
   <si>
-    <t>2025-08-21</t>
-  </si>
-  <si>
     <t>Coke Zero 180ml</t>
   </si>
   <si>
-    <t>2025-08-14</t>
-  </si>
-  <si>
     <t>Coke Zero 320ml</t>
   </si>
   <si>
-    <t>2025-07-30</t>
-  </si>
-  <si>
     <t>Coke Regular</t>
   </si>
   <si>
@@ -188,9 +176,6 @@
     <t>Prepared Foods</t>
   </si>
   <si>
-    <t>2025-06-08</t>
-  </si>
-  <si>
     <t>Wafello Italian Wafer</t>
   </si>
   <si>
@@ -200,9 +185,6 @@
     <t>piece</t>
   </si>
   <si>
-    <t>2025-10-08</t>
-  </si>
-  <si>
     <t>Six Fortune Sotanghon Noodles 500g</t>
   </si>
   <si>
@@ -236,9 +218,6 @@
     <t>Grains/Grain Products</t>
   </si>
   <si>
-    <t>2025-08-27</t>
-  </si>
-  <si>
     <t>Gumtect Toothpaste</t>
   </si>
   <si>
@@ -254,9 +233,6 @@
     <t>bottle</t>
   </si>
   <si>
-    <t>2025-10-06</t>
-  </si>
-  <si>
     <t>Colgate Total 12</t>
   </si>
   <si>
@@ -347,15 +323,9 @@
     <t>Sunsoya 3in1 Instant Macha</t>
   </si>
   <si>
-    <t>2025-09-15</t>
-  </si>
-  <si>
     <t>Magic Time Fat Free Buttered Popcorn 240g</t>
   </si>
   <si>
-    <t>2025-09-20</t>
-  </si>
-  <si>
     <t>Magic Time Flaming Hot Cheddar Popcorn 240g</t>
   </si>
   <si>
@@ -371,9 +341,6 @@
     <t>Mega Mexicana Nacho Chips</t>
   </si>
   <si>
-    <t>2025-09-26</t>
-  </si>
-  <si>
     <t>Reno Brand Liver Spread</t>
   </si>
   <si>
@@ -434,9 +401,6 @@
     <t>Confectionary</t>
   </si>
   <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
     <t>Nutridel Carrots &amp; Squash 120g</t>
   </si>
   <si>
@@ -449,9 +413,6 @@
     <t>Molinera Crushed Tomatoes 400g</t>
   </si>
   <si>
-    <t>2025-08-18</t>
-  </si>
-  <si>
     <t>Cream All Purpose Flour 200g</t>
   </si>
   <si>
@@ -563,18 +524,12 @@
     <t>649</t>
   </si>
   <si>
-    <t>2025-07-22</t>
-  </si>
-  <si>
     <t>Stik O Jr. Ube</t>
   </si>
   <si>
     <t>252</t>
   </si>
   <si>
-    <t>2025-09-10</t>
-  </si>
-  <si>
     <t>Stik o Choco Wafer 380g</t>
   </si>
   <si>
@@ -653,25 +608,25 @@
     <t>6636</t>
   </si>
   <si>
-    <t>2025-06-20</t>
-  </si>
-  <si>
     <t>Mi Sedaap Mi Sup Singapore Spicy Laksa</t>
   </si>
   <si>
     <t>2997</t>
   </si>
   <si>
-    <t>2025-06-25</t>
-  </si>
-  <si>
     <t>Mi Sedaap Mi Goreng 91G x 5</t>
   </si>
   <si>
     <t>1092</t>
   </si>
   <si>
-    <t>2025-06-18</t>
+    <t>2026-06-08</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>2025-10-29</t>
   </si>
 </sst>
 </file>
@@ -719,7 +674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -727,6 +682,10 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,7 +1032,7 @@
     <col min="8" max="8" width="14.140625" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" style="4" customWidth="1"/>
     <col min="12" max="12" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1108,7 +1067,7 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" s="2" t="s">
@@ -1146,7 +1105,7 @@
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="L2" t="s">
@@ -1184,7 +1143,7 @@
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="4" t="s">
         <v>22</v>
       </c>
       <c r="L3" t="s">
@@ -1222,7 +1181,7 @@
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L4" t="s">
@@ -1260,7 +1219,7 @@
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="4" t="s">
         <v>27</v>
       </c>
       <c r="L5" t="s">
@@ -1298,7 +1257,7 @@
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="L6" t="s">
@@ -1336,7 +1295,7 @@
       <c r="J7">
         <v>0</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" s="4" t="s">
         <v>31</v>
       </c>
       <c r="L7" t="s">
@@ -1374,8 +1333,8 @@
       <c r="J8">
         <v>0</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
+      <c r="K8" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L8" t="s">
         <v>20</v>
@@ -1395,7 +1354,7 @@
         <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
@@ -1412,8 +1371,8 @@
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9" t="s">
-        <v>35</v>
+      <c r="K9" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="L9" t="s">
         <v>20</v>
@@ -1433,7 +1392,7 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>24</v>
@@ -1450,8 +1409,8 @@
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
-        <v>37</v>
+      <c r="K10" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L10" t="s">
         <v>20</v>
@@ -1471,7 +1430,7 @@
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
         <v>24</v>
@@ -1488,8 +1447,8 @@
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11" t="s">
-        <v>39</v>
+      <c r="K11" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L11" t="s">
         <v>20</v>
@@ -1509,7 +1468,7 @@
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
         <v>24</v>
@@ -1526,8 +1485,8 @@
       <c r="J12">
         <v>0</v>
       </c>
-      <c r="K12" t="s">
-        <v>41</v>
+      <c r="K12" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L12" t="s">
         <v>20</v>
@@ -1547,7 +1506,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F13" t="s">
         <v>24</v>
@@ -1564,8 +1523,8 @@
       <c r="J13">
         <v>0</v>
       </c>
-      <c r="K13" t="s">
-        <v>43</v>
+      <c r="K13" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="L13" t="s">
         <v>20</v>
@@ -1585,16 +1544,16 @@
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I14">
         <v>0.22</v>
@@ -1602,8 +1561,8 @@
       <c r="J14">
         <v>0</v>
       </c>
-      <c r="K14" t="s">
-        <v>47</v>
+      <c r="K14" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -1623,16 +1582,16 @@
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I15">
         <v>0.12</v>
@@ -1640,8 +1599,8 @@
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15" t="s">
-        <v>50</v>
+      <c r="K15" s="4" t="s">
+        <v>194</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -1661,16 +1620,16 @@
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I16">
         <v>0.97</v>
@@ -1678,8 +1637,8 @@
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" t="s">
-        <v>54</v>
+      <c r="K16" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L16" t="s">
         <v>20</v>
@@ -1699,16 +1658,16 @@
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I17">
         <v>0.5</v>
@@ -1716,8 +1675,8 @@
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" t="s">
-        <v>57</v>
+      <c r="K17" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="L17" t="s">
         <v>20</v>
@@ -1737,16 +1696,16 @@
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I18">
         <v>0.5</v>
@@ -1754,8 +1713,8 @@
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18">
-        <v>0</v>
+      <c r="K18" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1775,16 +1734,16 @@
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I19">
         <v>0.5</v>
@@ -1792,8 +1751,8 @@
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19">
-        <v>0</v>
+      <c r="K19" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L19" t="s">
         <v>20</v>
@@ -1813,16 +1772,16 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1830,8 +1789,8 @@
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20">
-        <v>0</v>
+      <c r="K20" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L20" t="s">
         <v>20</v>
@@ -1851,16 +1810,16 @@
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="I21">
         <v>1.5</v>
@@ -1868,8 +1827,8 @@
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21">
-        <v>0</v>
+      <c r="K21" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L21" t="s">
         <v>20</v>
@@ -1889,16 +1848,16 @@
         <v>15</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1906,8 +1865,8 @@
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22" t="s">
-        <v>66</v>
+      <c r="K22" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1927,16 +1886,16 @@
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I23">
         <v>1.05</v>
@@ -1944,8 +1903,8 @@
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" t="s">
-        <v>69</v>
+      <c r="K23" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -1965,16 +1924,16 @@
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I24">
         <v>0.78</v>
@@ -1982,8 +1941,8 @@
       <c r="J24">
         <v>0</v>
       </c>
-      <c r="K24" t="s">
-        <v>72</v>
+      <c r="K24" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L24" t="s">
         <v>20</v>
@@ -2003,16 +1962,16 @@
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F25" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I25">
         <v>0.34</v>
@@ -2020,8 +1979,8 @@
       <c r="J25">
         <v>0</v>
       </c>
-      <c r="K25" t="s">
-        <v>74</v>
+      <c r="K25" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="L25" t="s">
         <v>20</v>
@@ -2041,16 +2000,16 @@
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I26">
         <v>0.79</v>
@@ -2058,8 +2017,8 @@
       <c r="J26">
         <v>0</v>
       </c>
-      <c r="K26" t="s">
-        <v>76</v>
+      <c r="K26" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="L26" t="s">
         <v>20</v>
@@ -2079,16 +2038,16 @@
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I27">
         <v>0.72</v>
@@ -2096,8 +2055,8 @@
       <c r="J27">
         <v>0</v>
       </c>
-      <c r="K27" t="s">
-        <v>78</v>
+      <c r="K27" s="4" t="s">
+        <v>70</v>
       </c>
       <c r="L27" t="s">
         <v>20</v>
@@ -2117,16 +2076,16 @@
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G28">
         <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I28">
         <v>2.78</v>
@@ -2134,8 +2093,8 @@
       <c r="J28">
         <v>0</v>
       </c>
-      <c r="K28" t="s">
-        <v>57</v>
+      <c r="K28" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="L28" t="s">
         <v>20</v>
@@ -2155,7 +2114,7 @@
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
         <v>24</v>
@@ -2164,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I29">
         <v>0.5</v>
@@ -2172,8 +2131,8 @@
       <c r="J29">
         <v>0</v>
       </c>
-      <c r="K29">
-        <v>0</v>
+      <c r="K29" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L29" t="s">
         <v>20</v>
@@ -2193,7 +2152,7 @@
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s">
         <v>24</v>
@@ -2202,7 +2161,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I30">
         <v>1.5</v>
@@ -2210,8 +2169,8 @@
       <c r="J30">
         <v>0</v>
       </c>
-      <c r="K30">
-        <v>0</v>
+      <c r="K30" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L30" t="s">
         <v>20</v>
@@ -2231,10 +2190,10 @@
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2248,8 +2207,8 @@
       <c r="J31">
         <v>0</v>
       </c>
-      <c r="K31" t="s">
-        <v>84</v>
+      <c r="K31" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L31" t="s">
         <v>20</v>
@@ -2269,16 +2228,16 @@
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I32">
         <v>0.13</v>
@@ -2286,8 +2245,8 @@
       <c r="J32">
         <v>0</v>
       </c>
-      <c r="K32" t="s">
-        <v>86</v>
+      <c r="K32" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
@@ -2307,16 +2266,16 @@
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I33">
         <v>0.18</v>
@@ -2324,8 +2283,8 @@
       <c r="J33">
         <v>0</v>
       </c>
-      <c r="K33" t="s">
-        <v>88</v>
+      <c r="K33" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="L33" t="s">
         <v>20</v>
@@ -2345,16 +2304,16 @@
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I34">
         <v>0.4</v>
@@ -2362,8 +2321,8 @@
       <c r="J34">
         <v>0</v>
       </c>
-      <c r="K34" t="s">
-        <v>54</v>
+      <c r="K34" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L34" t="s">
         <v>20</v>
@@ -2383,10 +2342,10 @@
         <v>15</v>
       </c>
       <c r="E35" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2400,8 +2359,8 @@
       <c r="J35">
         <v>0</v>
       </c>
-      <c r="K35" t="s">
-        <v>91</v>
+      <c r="K35" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -2421,10 +2380,10 @@
         <v>15</v>
       </c>
       <c r="E36" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F36" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2438,8 +2397,8 @@
       <c r="J36">
         <v>0</v>
       </c>
-      <c r="K36" t="s">
-        <v>94</v>
+      <c r="K36" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="L36" t="s">
         <v>20</v>
@@ -2459,10 +2418,10 @@
         <v>15</v>
       </c>
       <c r="E37" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G37">
         <v>3</v>
@@ -2476,8 +2435,8 @@
       <c r="J37">
         <v>0</v>
       </c>
-      <c r="K37" t="s">
-        <v>96</v>
+      <c r="K37" s="4" t="s">
+        <v>88</v>
       </c>
       <c r="L37" t="s">
         <v>20</v>
@@ -2497,16 +2456,16 @@
         <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F38" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I38">
         <v>0.59</v>
@@ -2514,8 +2473,8 @@
       <c r="J38">
         <v>0</v>
       </c>
-      <c r="K38" t="s">
-        <v>99</v>
+      <c r="K38" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="L38" t="s">
         <v>20</v>
@@ -2535,16 +2494,16 @@
         <v>15</v>
       </c>
       <c r="E39" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I39">
         <v>0.82</v>
@@ -2552,8 +2511,8 @@
       <c r="J39">
         <v>0</v>
       </c>
-      <c r="K39" t="s">
-        <v>101</v>
+      <c r="K39" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="L39" t="s">
         <v>20</v>
@@ -2573,16 +2532,16 @@
         <v>15</v>
       </c>
       <c r="E40" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I40">
         <v>0.5</v>
@@ -2590,8 +2549,8 @@
       <c r="J40">
         <v>0</v>
       </c>
-      <c r="K40" t="s">
-        <v>103</v>
+      <c r="K40" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L40" t="s">
         <v>20</v>
@@ -2611,16 +2570,16 @@
         <v>15</v>
       </c>
       <c r="E41" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I41">
         <v>0.28999999999999998</v>
@@ -2628,8 +2587,8 @@
       <c r="J41">
         <v>0</v>
       </c>
-      <c r="K41" t="s">
-        <v>105</v>
+      <c r="K41" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
@@ -2649,16 +2608,16 @@
         <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I42">
         <v>0.38</v>
@@ -2666,8 +2625,8 @@
       <c r="J42">
         <v>0</v>
       </c>
-      <c r="K42" t="s">
-        <v>105</v>
+      <c r="K42" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
@@ -2687,10 +2646,10 @@
         <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -2704,8 +2663,8 @@
       <c r="J43">
         <v>0</v>
       </c>
-      <c r="K43" t="s">
-        <v>108</v>
+      <c r="K43" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -2725,7 +2684,7 @@
         <v>15</v>
       </c>
       <c r="E44" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
         <v>24</v>
@@ -2742,8 +2701,8 @@
       <c r="J44">
         <v>0</v>
       </c>
-      <c r="K44" t="s">
-        <v>43</v>
+      <c r="K44" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L44" t="s">
         <v>20</v>
@@ -2763,16 +2722,16 @@
         <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I45">
         <v>0.53</v>
@@ -2780,8 +2739,8 @@
       <c r="J45">
         <v>0</v>
       </c>
-      <c r="K45" t="s">
-        <v>111</v>
+      <c r="K45" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L45" t="s">
         <v>20</v>
@@ -2801,10 +2760,10 @@
         <v>15</v>
       </c>
       <c r="E46" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="F46" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2818,8 +2777,8 @@
       <c r="J46">
         <v>0</v>
       </c>
-      <c r="K46" t="s">
-        <v>113</v>
+      <c r="K46" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="L46" t="s">
         <v>20</v>
@@ -2839,10 +2798,10 @@
         <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F47" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2856,8 +2815,8 @@
       <c r="J47">
         <v>0</v>
       </c>
-      <c r="K47" t="s">
-        <v>115</v>
+      <c r="K47" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="L47" t="s">
         <v>20</v>
@@ -2877,10 +2836,10 @@
         <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F48" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2894,8 +2853,8 @@
       <c r="J48">
         <v>0</v>
       </c>
-      <c r="K48" t="s">
-        <v>118</v>
+      <c r="K48" s="4" t="s">
+        <v>107</v>
       </c>
       <c r="L48" t="s">
         <v>20</v>
@@ -2915,10 +2874,10 @@
         <v>15</v>
       </c>
       <c r="E49" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F49" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G49">
         <v>16</v>
@@ -2932,8 +2891,8 @@
       <c r="J49">
         <v>0</v>
       </c>
-      <c r="K49" t="s">
-        <v>120</v>
+      <c r="K49" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="L49" t="s">
         <v>20</v>
@@ -2953,16 +2912,16 @@
         <v>15</v>
       </c>
       <c r="E50" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="F50" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I50">
         <v>0.05</v>
@@ -2970,8 +2929,8 @@
       <c r="J50">
         <v>0</v>
       </c>
-      <c r="K50" t="s">
-        <v>122</v>
+      <c r="K50" s="4" t="s">
+        <v>111</v>
       </c>
       <c r="L50" t="s">
         <v>20</v>
@@ -2991,16 +2950,16 @@
         <v>15</v>
       </c>
       <c r="E51" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F51" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G51">
         <v>4</v>
       </c>
       <c r="H51" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I51">
         <v>1.76</v>
@@ -3008,8 +2967,8 @@
       <c r="J51">
         <v>0</v>
       </c>
-      <c r="K51" t="s">
-        <v>124</v>
+      <c r="K51" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="L51" t="s">
         <v>20</v>
@@ -3029,16 +2988,16 @@
         <v>15</v>
       </c>
       <c r="E52" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F52" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I52">
         <v>0.2</v>
@@ -3046,8 +3005,8 @@
       <c r="J52">
         <v>0</v>
       </c>
-      <c r="K52" t="s">
-        <v>126</v>
+      <c r="K52" s="4" t="s">
+        <v>115</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
@@ -3067,16 +3026,16 @@
         <v>15</v>
       </c>
       <c r="E53" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F53" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I53">
         <v>2</v>
@@ -3084,8 +3043,8 @@
       <c r="J53">
         <v>0</v>
       </c>
-      <c r="K53" t="s">
-        <v>129</v>
+      <c r="K53" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="L53" t="s">
         <v>20</v>
@@ -3105,16 +3064,16 @@
         <v>15</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F54" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I54">
         <v>0.45</v>
@@ -3122,8 +3081,8 @@
       <c r="J54">
         <v>0</v>
       </c>
-      <c r="K54" t="s">
-        <v>132</v>
+      <c r="K54" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
@@ -3143,16 +3102,16 @@
         <v>15</v>
       </c>
       <c r="E55" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="F55" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="G55">
         <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I55">
         <v>1.3</v>
@@ -3160,8 +3119,8 @@
       <c r="J55">
         <v>0</v>
       </c>
-      <c r="K55" t="s">
-        <v>135</v>
+      <c r="K55" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="L55" t="s">
         <v>20</v>
@@ -3181,10 +3140,10 @@
         <v>15</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="F56" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -3198,8 +3157,8 @@
       <c r="J56">
         <v>0</v>
       </c>
-      <c r="K56" t="s">
-        <v>137</v>
+      <c r="K56" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L56" t="s">
         <v>20</v>
@@ -3219,16 +3178,16 @@
         <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="F57" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I57">
         <v>0.27</v>
@@ -3236,8 +3195,8 @@
       <c r="J57">
         <v>0</v>
       </c>
-      <c r="K57" t="s">
-        <v>139</v>
+      <c r="K57" s="4" t="s">
+        <v>126</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -3257,16 +3216,16 @@
         <v>15</v>
       </c>
       <c r="E58" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="F58" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I58">
         <v>0.46</v>
@@ -3274,8 +3233,8 @@
       <c r="J58">
         <v>0</v>
       </c>
-      <c r="K58" t="s">
-        <v>141</v>
+      <c r="K58" s="4" t="s">
+        <v>128</v>
       </c>
       <c r="L58" t="s">
         <v>20</v>
@@ -3295,16 +3254,16 @@
         <v>15</v>
       </c>
       <c r="E59" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F59" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I59">
         <v>0.05</v>
@@ -3312,8 +3271,8 @@
       <c r="J59">
         <v>0</v>
       </c>
-      <c r="K59" t="s">
-        <v>143</v>
+      <c r="K59" s="4" t="s">
+        <v>130</v>
       </c>
       <c r="L59" t="s">
         <v>20</v>
@@ -3333,10 +3292,10 @@
         <v>15</v>
       </c>
       <c r="E60" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="F60" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -3350,8 +3309,8 @@
       <c r="J60">
         <v>0</v>
       </c>
-      <c r="K60" t="s">
-        <v>145</v>
+      <c r="K60" s="4" t="s">
+        <v>132</v>
       </c>
       <c r="L60" t="s">
         <v>20</v>
@@ -3371,16 +3330,16 @@
         <v>15</v>
       </c>
       <c r="E61" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I61">
         <v>0.63</v>
@@ -3388,8 +3347,8 @@
       <c r="J61">
         <v>0</v>
       </c>
-      <c r="K61" t="s">
-        <v>147</v>
+      <c r="K61" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="L61" t="s">
         <v>20</v>
@@ -3409,16 +3368,16 @@
         <v>15</v>
       </c>
       <c r="E62" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="F62" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="G62">
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I62">
         <v>1.1200000000000001</v>
@@ -3426,8 +3385,8 @@
       <c r="J62">
         <v>0</v>
       </c>
-      <c r="K62" t="s">
-        <v>149</v>
+      <c r="K62" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="L62" t="s">
         <v>20</v>
@@ -3447,16 +3406,16 @@
         <v>15</v>
       </c>
       <c r="E63" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I63">
         <v>0.13</v>
@@ -3464,8 +3423,8 @@
       <c r="J63">
         <v>0</v>
       </c>
-      <c r="K63" t="s">
-        <v>151</v>
+      <c r="K63" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="L63" t="s">
         <v>20</v>
@@ -3485,16 +3444,16 @@
         <v>15</v>
       </c>
       <c r="E64" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="F64" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I64">
         <v>0.65</v>
@@ -3502,8 +3461,8 @@
       <c r="J64">
         <v>0</v>
       </c>
-      <c r="K64" t="s">
-        <v>153</v>
+      <c r="K64" s="4" t="s">
+        <v>140</v>
       </c>
       <c r="L64" t="s">
         <v>20</v>
@@ -3523,10 +3482,10 @@
         <v>15</v>
       </c>
       <c r="E65" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="F65" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G65">
         <v>3</v>
@@ -3540,8 +3499,8 @@
       <c r="J65">
         <v>0</v>
       </c>
-      <c r="K65" t="s">
-        <v>155</v>
+      <c r="K65" s="4" t="s">
+        <v>142</v>
       </c>
       <c r="L65" t="s">
         <v>20</v>
@@ -3561,10 +3520,10 @@
         <v>15</v>
       </c>
       <c r="E66" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="F66" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G66">
         <v>11</v>
@@ -3578,8 +3537,8 @@
       <c r="J66">
         <v>0</v>
       </c>
-      <c r="K66" t="s">
-        <v>157</v>
+      <c r="K66" s="4" t="s">
+        <v>144</v>
       </c>
       <c r="L66" t="s">
         <v>20</v>
@@ -3599,7 +3558,7 @@
         <v>15</v>
       </c>
       <c r="E67" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="F67" t="s">
         <v>17</v>
@@ -3608,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I67">
         <v>0.56999999999999995</v>
@@ -3616,8 +3575,8 @@
       <c r="J67">
         <v>0</v>
       </c>
-      <c r="K67">
-        <v>0</v>
+      <c r="K67" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L67" t="s">
         <v>20</v>
@@ -3637,16 +3596,16 @@
         <v>15</v>
       </c>
       <c r="E68" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="F68" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I68">
         <v>1.29</v>
@@ -3654,8 +3613,8 @@
       <c r="J68">
         <v>0</v>
       </c>
-      <c r="K68" t="s">
-        <v>160</v>
+      <c r="K68" s="4" t="s">
+        <v>147</v>
       </c>
       <c r="L68" t="s">
         <v>20</v>
@@ -3675,25 +3634,25 @@
         <v>15</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="F69" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I69">
         <v>0.45</v>
       </c>
       <c r="J69" t="s">
-        <v>162</v>
-      </c>
-      <c r="K69" t="s">
-        <v>163</v>
+        <v>149</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="L69" t="s">
         <v>20</v>
@@ -3713,25 +3672,25 @@
         <v>15</v>
       </c>
       <c r="E70" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F70" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I70">
         <v>0.14000000000000001</v>
       </c>
       <c r="J70" t="s">
-        <v>165</v>
-      </c>
-      <c r="K70" t="s">
-        <v>166</v>
+        <v>152</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>153</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
@@ -3751,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="E71" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="F71" t="s">
         <v>24</v>
@@ -3766,10 +3725,10 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="J71" t="s">
-        <v>168</v>
-      </c>
-      <c r="K71" t="s">
-        <v>88</v>
+        <v>155</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L71" t="s">
         <v>20</v>
@@ -3789,25 +3748,25 @@
         <v>15</v>
       </c>
       <c r="E72" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="F72" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I72">
         <v>0.25</v>
       </c>
       <c r="J72" t="s">
-        <v>170</v>
-      </c>
-      <c r="K72" t="s">
-        <v>171</v>
+        <v>157</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="L72" t="s">
         <v>20</v>
@@ -3827,25 +3786,25 @@
         <v>15</v>
       </c>
       <c r="E73" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="F73" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I73">
         <v>0.25</v>
       </c>
       <c r="J73" t="s">
-        <v>170</v>
-      </c>
-      <c r="K73" t="s">
-        <v>171</v>
+        <v>157</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>158</v>
       </c>
       <c r="L73" t="s">
         <v>20</v>
@@ -3865,10 +3824,10 @@
         <v>15</v>
       </c>
       <c r="E74" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="F74" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G74">
         <v>11</v>
@@ -3880,10 +3839,10 @@
         <v>3.85</v>
       </c>
       <c r="J74" t="s">
-        <v>174</v>
-      </c>
-      <c r="K74" t="s">
-        <v>175</v>
+        <v>161</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L74" t="s">
         <v>20</v>
@@ -3903,25 +3862,25 @@
         <v>15</v>
       </c>
       <c r="E75" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I75">
         <v>1.2</v>
       </c>
       <c r="J75" t="s">
-        <v>177</v>
-      </c>
-      <c r="K75" t="s">
-        <v>178</v>
+        <v>163</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L75" t="s">
         <v>20</v>
@@ -3941,25 +3900,25 @@
         <v>15</v>
       </c>
       <c r="E76" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="F76" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="I76">
         <v>0.44</v>
       </c>
       <c r="J76" t="s">
-        <v>180</v>
-      </c>
-      <c r="K76" t="s">
-        <v>101</v>
+        <v>165</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>93</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
@@ -3979,10 +3938,10 @@
         <v>15</v>
       </c>
       <c r="E77" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="F77" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3994,10 +3953,10 @@
         <v>0.31</v>
       </c>
       <c r="J77" t="s">
-        <v>182</v>
-      </c>
-      <c r="K77" t="s">
-        <v>183</v>
+        <v>167</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>168</v>
       </c>
       <c r="L77" t="s">
         <v>20</v>
@@ -4017,10 +3976,10 @@
         <v>15</v>
       </c>
       <c r="E78" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F78" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G78">
         <v>3</v>
@@ -4032,10 +3991,10 @@
         <v>1.3</v>
       </c>
       <c r="J78" t="s">
-        <v>185</v>
-      </c>
-      <c r="K78" t="s">
-        <v>186</v>
+        <v>170</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="L78" t="s">
         <v>20</v>
@@ -4055,16 +4014,16 @@
         <v>15</v>
       </c>
       <c r="E79" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F79" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G79">
         <v>3</v>
       </c>
       <c r="H79" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="I79">
         <v>30</v>
@@ -4072,8 +4031,8 @@
       <c r="J79">
         <v>0</v>
       </c>
-      <c r="K79" t="s">
-        <v>188</v>
+      <c r="K79" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="L79" t="s">
         <v>20</v>
@@ -4093,25 +4052,25 @@
         <v>15</v>
       </c>
       <c r="E80" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="F80" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I80">
         <v>0.53</v>
       </c>
       <c r="J80" t="s">
-        <v>190</v>
-      </c>
-      <c r="K80" t="s">
-        <v>47</v>
+        <v>175</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
@@ -4131,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="E81" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F81" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G81">
         <v>2</v>
@@ -4146,10 +4105,10 @@
         <v>0.36</v>
       </c>
       <c r="J81" t="s">
-        <v>192</v>
-      </c>
-      <c r="K81" t="s">
-        <v>129</v>
+        <v>177</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="L81" t="s">
         <v>20</v>
@@ -4169,7 +4128,7 @@
         <v>15</v>
       </c>
       <c r="E82" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F82" t="s">
         <v>24</v>
@@ -4184,10 +4143,10 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="J82" t="s">
-        <v>194</v>
-      </c>
-      <c r="K82" t="s">
-        <v>84</v>
+        <v>179</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="L82" t="s">
         <v>20</v>
@@ -4207,10 +4166,10 @@
         <v>15</v>
       </c>
       <c r="E83" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F83" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G83">
         <v>2</v>
@@ -4222,10 +4181,10 @@
         <v>0.26</v>
       </c>
       <c r="J83" t="s">
-        <v>196</v>
-      </c>
-      <c r="K83" t="s">
-        <v>129</v>
+        <v>181</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="L83" t="s">
         <v>20</v>
@@ -4245,10 +4204,10 @@
         <v>15</v>
       </c>
       <c r="E84" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F84" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G84">
         <v>7</v>
@@ -4260,10 +4219,10 @@
         <v>3.15</v>
       </c>
       <c r="J84" t="s">
-        <v>198</v>
-      </c>
-      <c r="K84" t="s">
-        <v>199</v>
+        <v>183</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="L84" t="s">
         <v>20</v>
@@ -4271,28 +4230,28 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
       </c>
       <c r="C85" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D85" t="s">
         <v>15</v>
       </c>
       <c r="E85" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F85" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G85">
         <v>8352</v>
       </c>
       <c r="H85" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I85">
         <v>47371</v>
@@ -4300,8 +4259,8 @@
       <c r="J85">
         <v>0</v>
       </c>
-      <c r="K85">
-        <v>0</v>
+      <c r="K85" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L85" t="s">
         <v>20</v>
@@ -4309,37 +4268,37 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
       </c>
       <c r="C86" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D86" t="s">
         <v>15</v>
       </c>
       <c r="E86" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F86" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G86">
         <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I86">
         <v>11.91</v>
       </c>
       <c r="J86" t="s">
-        <v>204</v>
-      </c>
-      <c r="K86" t="s">
-        <v>205</v>
+        <v>189</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L86" t="s">
         <v>20</v>
@@ -4347,37 +4306,37 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
       </c>
       <c r="C87" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D87" t="s">
         <v>15</v>
       </c>
       <c r="E87" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="F87" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G87">
         <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="I87">
         <v>8.93</v>
       </c>
       <c r="J87" t="s">
-        <v>207</v>
-      </c>
-      <c r="K87" t="s">
-        <v>208</v>
+        <v>191</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="L87" t="s">
         <v>20</v>
@@ -4385,37 +4344,37 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
       </c>
       <c r="C88" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D88" t="s">
         <v>15</v>
       </c>
       <c r="E88" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="F88" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G88">
         <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I88">
         <v>10.27</v>
       </c>
       <c r="J88" t="s">
-        <v>210</v>
-      </c>
-      <c r="K88" t="s">
-        <v>211</v>
+        <v>193</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>196</v>
       </c>
       <c r="L88" t="s">
         <v>20</v>

--- a/FoodBank Files/Product In.xlsx
+++ b/FoodBank Files/Product In.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icarusjay\Downloads\xampp\htdocs\FoodBank Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D120A4DC-8713-44D5-9F08-8DF8273EF21A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F155499-66E5-4F37-8F88-7A515966A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{FEF8D386-D128-4069-BDCD-FE457B1D9085}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="180">
   <si>
     <t>ENTRY DATE</t>
   </si>
@@ -62,9 +62,6 @@
     <t>PACKED BY</t>
   </si>
   <si>
-    <t>TOTAL WEIGHT(KG)</t>
-  </si>
-  <si>
     <t>TOTAL COST(₱)</t>
   </si>
   <si>
@@ -485,33 +482,21 @@
     <t>UCC 3in1 Coffee Regular</t>
   </si>
   <si>
-    <t>242</t>
-  </si>
-  <si>
     <t>2026-05-29</t>
   </si>
   <si>
     <t>UCC 3in1 Blend</t>
   </si>
   <si>
-    <t>288</t>
-  </si>
-  <si>
     <t>2026-08-11</t>
   </si>
   <si>
     <t>Doctor Pepper 355ml</t>
   </si>
   <si>
-    <t>455</t>
-  </si>
-  <si>
     <t>Nescafe Dolce Gusto</t>
   </si>
   <si>
-    <t>499</t>
-  </si>
-  <si>
     <t>2025-11-10</t>
   </si>
   <si>
@@ -521,36 +506,21 @@
     <t>Canada Dry Ginger</t>
   </si>
   <si>
-    <t>649</t>
-  </si>
-  <si>
     <t>Stik O Jr. Ube</t>
   </si>
   <si>
-    <t>252</t>
-  </si>
-  <si>
     <t>Stik o Choco Wafer 380g</t>
   </si>
   <si>
-    <t>84</t>
-  </si>
-  <si>
     <t>Delimondo Caldereta 260g</t>
   </si>
   <si>
-    <t>149</t>
-  </si>
-  <si>
     <t>2027-02-20</t>
   </si>
   <si>
     <t>Delimondo Garlic Chili 380g</t>
   </si>
   <si>
-    <t>594</t>
-  </si>
-  <si>
     <t>2027-08-22</t>
   </si>
   <si>
@@ -563,33 +533,18 @@
     <t>Milkita Lollipop</t>
   </si>
   <si>
-    <t>227</t>
-  </si>
-  <si>
     <t>Saba Premium Mackerel</t>
   </si>
   <si>
-    <t>70.40</t>
-  </si>
-  <si>
     <t>Welch White Grape</t>
   </si>
   <si>
-    <t>165</t>
-  </si>
-  <si>
     <t>Unipak Mackerel Natural Oil 155g</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>Sunbest Whole Kernel Corn 425g</t>
   </si>
   <si>
-    <t>318.50</t>
-  </si>
-  <si>
     <t>2026-07-26</t>
   </si>
   <si>
@@ -605,21 +560,12 @@
     <t>Want Want Senbei Family Pack 520G x 5</t>
   </si>
   <si>
-    <t>6636</t>
-  </si>
-  <si>
     <t>Mi Sedaap Mi Sup Singapore Spicy Laksa</t>
   </si>
   <si>
-    <t>2997</t>
-  </si>
-  <si>
     <t>Mi Sedaap Mi Goreng 91G x 5</t>
   </si>
   <si>
-    <t>1092</t>
-  </si>
-  <si>
     <t>2026-06-08</t>
   </si>
   <si>
@@ -627,6 +573,9 @@
   </si>
   <si>
     <t>2025-10-29</t>
+  </si>
+  <si>
+    <t>WEIGHT(KG)</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +976,10 @@
     <col min="2" max="2" width="27.28515625" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" customWidth="1"/>
     <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
     <col min="11" max="11" width="11.42578125" style="4" customWidth="1"/>
     <col min="12" max="12" width="13.85546875" customWidth="1"/>
@@ -1062,118 +1011,118 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>0.33</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I2">
-        <v>0.65</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>24</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4">
         <v>0.35</v>
@@ -1182,36 +1131,36 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5">
         <v>0.35</v>
@@ -1220,36 +1169,36 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I6">
         <v>0.35</v>
@@ -1258,302 +1207,302 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7">
-        <v>0.85</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I8">
-        <v>0.98</v>
+        <v>0.33</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I9">
-        <v>2.3199999999999998</v>
+        <v>0.33</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G11">
         <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I11">
-        <v>1.1000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12">
-        <v>9.15</v>
+        <v>0.34</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G13">
         <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I13">
-        <v>16.190000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" t="s">
         <v>40</v>
-      </c>
-      <c r="F14" t="s">
-        <v>41</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I14">
         <v>0.22</v>
@@ -1562,36 +1511,36 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" t="s">
         <v>44</v>
-      </c>
-      <c r="F15" t="s">
-        <v>45</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I15">
         <v>0.12</v>
@@ -1600,74 +1549,74 @@
         <v>0</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" t="s">
         <v>46</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I16">
-        <v>0.97</v>
+        <v>0.24</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I17">
         <v>0.5</v>
@@ -1676,36 +1625,36 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
         <v>52</v>
-      </c>
-      <c r="F18" t="s">
-        <v>53</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I18">
         <v>0.5</v>
@@ -1714,36 +1663,36 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I19">
         <v>0.5</v>
@@ -1752,36 +1701,36 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1790,74 +1739,74 @@
         <v>0</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I21">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" t="s">
         <v>58</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1866,112 +1815,112 @@
         <v>0</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
+        <v>59</v>
+      </c>
+      <c r="F23" t="s">
         <v>60</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I23">
-        <v>1.05</v>
+        <v>0.35</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I24">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I25">
         <v>0.34</v>
@@ -1980,36 +1929,36 @@
         <v>0</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I26">
         <v>0.79</v>
@@ -2018,112 +1967,112 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I27">
-        <v>0.72</v>
+        <v>0.36</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G28">
         <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I28">
-        <v>2.78</v>
+        <v>0.4</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I29">
         <v>0.5</v>
@@ -2132,36 +2081,36 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I30">
         <v>1.5</v>
@@ -2170,36 +2119,36 @@
         <v>0</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E31" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" t="s">
         <v>74</v>
-      </c>
-      <c r="F31" t="s">
-        <v>75</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I31">
         <v>0.45</v>
@@ -2208,36 +2157,36 @@
         <v>0</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I32">
         <v>0.13</v>
@@ -2246,36 +2195,36 @@
         <v>0</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I33">
         <v>0.18</v>
@@ -2284,36 +2233,36 @@
         <v>0</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I34">
         <v>0.4</v>
@@ -2322,36 +2271,36 @@
         <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I35">
         <v>0.28000000000000003</v>
@@ -2360,112 +2309,112 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" t="s">
         <v>84</v>
-      </c>
-      <c r="F36" t="s">
-        <v>85</v>
       </c>
       <c r="G36">
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I36">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I37">
-        <v>1.27</v>
+        <v>0.42</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" t="s">
         <v>89</v>
-      </c>
-      <c r="F38" t="s">
-        <v>90</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I38">
         <v>0.59</v>
@@ -2474,36 +2423,36 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E39" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I39">
         <v>0.82</v>
@@ -2512,74 +2461,74 @@
         <v>0</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I40">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L40" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I41">
         <v>0.28999999999999998</v>
@@ -2588,112 +2537,112 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L41" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I42">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F43" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G43">
         <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I43">
-        <v>1.1499999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I44">
         <v>0.35</v>
@@ -2702,74 +2651,74 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E45" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I45">
-        <v>0.53</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D46" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E46" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I46">
         <v>0.12</v>
@@ -2778,36 +2727,36 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I47">
         <v>0.43</v>
@@ -2816,36 +2765,36 @@
         <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L47" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E48" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" t="s">
         <v>105</v>
-      </c>
-      <c r="F48" t="s">
-        <v>106</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I48">
         <v>0.87</v>
@@ -2854,74 +2803,74 @@
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G49">
         <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I49">
-        <v>3.52</v>
+        <v>0.22</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L49" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E50" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I50">
         <v>0.05</v>
@@ -2930,74 +2879,74 @@
         <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G51">
         <v>4</v>
       </c>
       <c r="H51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I51">
-        <v>1.76</v>
+        <v>0.44</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I52">
         <v>0.2</v>
@@ -3006,36 +2955,36 @@
         <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F53" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I53">
         <v>2</v>
@@ -3044,150 +2993,150 @@
         <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E54" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" t="s">
         <v>119</v>
-      </c>
-      <c r="F54" t="s">
-        <v>120</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I54">
-        <v>0.45</v>
+        <v>0.22500000000000001</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E55" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" t="s">
         <v>121</v>
-      </c>
-      <c r="F55" t="s">
-        <v>122</v>
       </c>
       <c r="G55">
         <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I55">
-        <v>1.3</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E56" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G56">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I56">
-        <v>1.8</v>
+        <v>0.2</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F57" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I57">
         <v>0.27</v>
@@ -3196,36 +3145,36 @@
         <v>0</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L57" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D58" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I58">
         <v>0.46</v>
@@ -3234,36 +3183,36 @@
         <v>0</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L58" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I59">
         <v>0.05</v>
@@ -3272,36 +3221,36 @@
         <v>0</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E60" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I60">
         <v>0.13</v>
@@ -3310,264 +3259,264 @@
         <v>0</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F61" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I61">
-        <v>0.63</v>
+        <v>0.21</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G62">
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I62">
-        <v>1.1200000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I63">
-        <v>0.13</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E64" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F64" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I64">
-        <v>0.65</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E65" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
       <c r="H65" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I65">
-        <v>1.78</v>
+        <v>0.59</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E66" t="s">
+        <v>142</v>
+      </c>
+      <c r="F66" t="s">
+        <v>84</v>
+      </c>
+      <c r="G66">
+        <v>11</v>
+      </c>
+      <c r="H66" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66">
+        <v>0.42</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F66" t="s">
-        <v>85</v>
-      </c>
-      <c r="G66">
-        <v>11</v>
-      </c>
-      <c r="H66" t="s">
-        <v>18</v>
-      </c>
-      <c r="I66">
-        <v>4.62</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="L66" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E67" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I67">
         <v>0.56999999999999995</v>
@@ -3576,808 +3525,808 @@
         <v>0</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E68" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I68">
-        <v>1.29</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I69">
-        <v>0.45</v>
-      </c>
-      <c r="J69" t="s">
-        <v>149</v>
+        <v>0.22500000000000001</v>
+      </c>
+      <c r="J69">
+        <v>121</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E70" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I70">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="J70" t="s">
-        <v>152</v>
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="J70">
+        <v>144</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F71" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I71">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="J71" t="s">
-        <v>155</v>
+        <v>0.377</v>
+      </c>
+      <c r="J71">
+        <v>75.83</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D72" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E72" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I72">
         <v>0.25</v>
       </c>
-      <c r="J72" t="s">
-        <v>157</v>
+      <c r="J72">
+        <v>499</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I73">
         <v>0.25</v>
       </c>
-      <c r="J73" t="s">
-        <v>157</v>
+      <c r="J73">
+        <v>499</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="L73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G74">
         <v>11</v>
       </c>
       <c r="H74" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I74">
-        <v>3.85</v>
-      </c>
-      <c r="J74" t="s">
-        <v>161</v>
+        <v>0.35</v>
+      </c>
+      <c r="J74">
+        <v>59</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I75">
-        <v>1.2</v>
-      </c>
-      <c r="J75" t="s">
-        <v>163</v>
+        <v>0.4</v>
+      </c>
+      <c r="J75">
+        <v>84</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L75" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E76" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F76" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I76">
         <v>0.44</v>
       </c>
-      <c r="J76" t="s">
-        <v>165</v>
+      <c r="J76">
+        <v>84</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E77" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I77">
         <v>0.31</v>
       </c>
-      <c r="J77" t="s">
-        <v>167</v>
+      <c r="J77">
+        <v>149</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="L77" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E78" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I78">
-        <v>1.3</v>
-      </c>
-      <c r="J78" t="s">
-        <v>170</v>
+        <v>0.433</v>
+      </c>
+      <c r="J78">
+        <v>198</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="F79" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G79">
         <v>3</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I79">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I80">
         <v>0.53</v>
       </c>
-      <c r="J80" t="s">
-        <v>175</v>
+      <c r="J80">
+        <v>227</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F81" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G81">
         <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I81">
-        <v>0.36</v>
-      </c>
-      <c r="J81" t="s">
-        <v>177</v>
+        <v>0.18</v>
+      </c>
+      <c r="J81">
+        <v>35.200000000000003</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E82" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="F82" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G82">
         <v>3</v>
       </c>
       <c r="H82" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I82">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="J82" t="s">
-        <v>179</v>
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="J82">
+        <v>55</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E83" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="F83" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I83">
-        <v>0.26</v>
-      </c>
-      <c r="J83" t="s">
-        <v>181</v>
+        <v>0.13</v>
+      </c>
+      <c r="J83">
+        <v>35</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E84" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="F84" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G84">
         <v>7</v>
       </c>
       <c r="H84" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I84">
-        <v>3.15</v>
-      </c>
-      <c r="J84" t="s">
-        <v>183</v>
+        <v>0.45</v>
+      </c>
+      <c r="J84">
+        <v>45.5</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C85" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D85" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F85" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G85">
         <v>8352</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I85">
-        <v>47371</v>
+        <v>0.18</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C86" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="F86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G86">
         <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I86">
-        <v>11.91</v>
-      </c>
-      <c r="J86" t="s">
-        <v>189</v>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="J86">
+        <v>316</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C87" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="F87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G87">
         <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I87">
-        <v>8.93</v>
-      </c>
-      <c r="J87" t="s">
-        <v>191</v>
+        <v>0.33</v>
+      </c>
+      <c r="J87">
+        <v>111</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="L87" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="B88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E88" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G88">
         <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I88">
-        <v>10.27</v>
-      </c>
-      <c r="J88" t="s">
-        <v>193</v>
+        <v>0.86</v>
+      </c>
+      <c r="J88">
+        <v>91</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="L88" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/FoodBank Files/Product In.xlsx
+++ b/FoodBank Files/Product In.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icarusjay\Downloads\xampp\htdocs\FoodBank Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F155499-66E5-4F37-8F88-7A515966A58B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3459C4-2004-4A92-965F-730AF53B9A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{FEF8D386-D128-4069-BDCD-FE457B1D9085}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>PACKED BY</t>
   </si>
   <si>
-    <t>TOTAL COST(₱)</t>
-  </si>
-  <si>
     <t>EXPIRY DATE</t>
   </si>
   <si>
@@ -576,6 +573,9 @@
   </si>
   <si>
     <t>WEIGHT(KG)</t>
+  </si>
+  <si>
+    <t>COST</t>
   </si>
 </sst>
 </file>
@@ -1011,42 +1011,42 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
       </c>
       <c r="G2">
         <v>2</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2">
         <v>0.33</v>
@@ -1055,36 +1055,36 @@
         <v>0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3">
         <v>0.33</v>
@@ -1093,36 +1093,36 @@
         <v>0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
         <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4">
         <v>0.35</v>
@@ -1131,36 +1131,36 @@
         <v>0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5">
         <v>0.35</v>
@@ -1169,36 +1169,36 @@
         <v>0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6">
         <v>0.35</v>
@@ -1207,36 +1207,36 @@
         <v>0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
       <c r="H7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7">
         <v>0.28000000000000003</v>
@@ -1245,36 +1245,36 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G8">
         <v>3</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8">
         <v>0.33</v>
@@ -1283,36 +1283,36 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9">
         <v>7</v>
       </c>
       <c r="H9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9">
         <v>0.33</v>
@@ -1321,36 +1321,36 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10">
         <v>0.33</v>
@@ -1359,36 +1359,36 @@
         <v>0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11">
         <v>6</v>
       </c>
       <c r="H11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11">
         <v>0.18</v>
@@ -1397,36 +1397,36 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12">
         <v>27</v>
       </c>
       <c r="H12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12">
         <v>0.34</v>
@@ -1435,36 +1435,36 @@
         <v>0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13">
         <v>44</v>
       </c>
       <c r="H13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13">
         <v>0.36</v>
@@ -1473,36 +1473,36 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" t="s">
         <v>39</v>
-      </c>
-      <c r="F14" t="s">
-        <v>40</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I14">
         <v>0.22</v>
@@ -1511,36 +1511,36 @@
         <v>0</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
+        <v>42</v>
+      </c>
+      <c r="F15" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" t="s">
-        <v>44</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I15">
         <v>0.12</v>
@@ -1549,36 +1549,36 @@
         <v>0</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
         <v>45</v>
-      </c>
-      <c r="F16" t="s">
-        <v>46</v>
       </c>
       <c r="G16">
         <v>4</v>
       </c>
       <c r="H16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I16">
         <v>0.24</v>
@@ -1587,36 +1587,36 @@
         <v>0</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I17">
         <v>0.5</v>
@@ -1625,36 +1625,36 @@
         <v>0</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L17" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" t="s">
+        <v>50</v>
+      </c>
+      <c r="F18" t="s">
         <v>51</v>
-      </c>
-      <c r="F18" t="s">
-        <v>52</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I18">
         <v>0.5</v>
@@ -1663,36 +1663,36 @@
         <v>0</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I19">
         <v>0.5</v>
@@ -1701,36 +1701,36 @@
         <v>0</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -1739,36 +1739,36 @@
         <v>0</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I21">
         <v>0.5</v>
@@ -1777,36 +1777,36 @@
         <v>0</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" t="s">
         <v>57</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22">
         <v>1</v>
@@ -1815,36 +1815,36 @@
         <v>0</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" t="s">
         <v>59</v>
-      </c>
-      <c r="F23" t="s">
-        <v>60</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I23">
         <v>0.35</v>
@@ -1853,36 +1853,36 @@
         <v>0</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I24">
         <v>0.39</v>
@@ -1891,36 +1891,36 @@
         <v>0</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G25">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I25">
         <v>0.34</v>
@@ -1929,36 +1929,36 @@
         <v>0</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L25" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I26">
         <v>0.79</v>
@@ -1967,36 +1967,36 @@
         <v>0</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G27">
         <v>2</v>
       </c>
       <c r="H27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I27">
         <v>0.36</v>
@@ -2005,36 +2005,36 @@
         <v>0</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L27" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G28">
         <v>7</v>
       </c>
       <c r="H28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I28">
         <v>0.4</v>
@@ -2043,36 +2043,36 @@
         <v>0</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I29">
         <v>0.5</v>
@@ -2081,36 +2081,36 @@
         <v>0</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I30">
         <v>1.5</v>
@@ -2119,36 +2119,36 @@
         <v>0</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E31" t="s">
+        <v>72</v>
+      </c>
+      <c r="F31" t="s">
         <v>73</v>
-      </c>
-      <c r="F31" t="s">
-        <v>74</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31">
         <v>0.45</v>
@@ -2157,36 +2157,36 @@
         <v>0</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
       <c r="H32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I32">
         <v>0.13</v>
@@ -2195,36 +2195,36 @@
         <v>0</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I33">
         <v>0.18</v>
@@ -2233,36 +2233,36 @@
         <v>0</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I34">
         <v>0.4</v>
@@ -2271,36 +2271,36 @@
         <v>0</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F35" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35">
         <v>0.28000000000000003</v>
@@ -2309,36 +2309,36 @@
         <v>0</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E36" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" t="s">
         <v>83</v>
-      </c>
-      <c r="F36" t="s">
-        <v>84</v>
       </c>
       <c r="G36">
         <v>2</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36">
         <v>0.2</v>
@@ -2347,36 +2347,36 @@
         <v>0</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="H37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37">
         <v>0.42</v>
@@ -2385,36 +2385,36 @@
         <v>0</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" t="s">
         <v>88</v>
-      </c>
-      <c r="F38" t="s">
-        <v>89</v>
       </c>
       <c r="G38">
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I38">
         <v>0.59</v>
@@ -2423,36 +2423,36 @@
         <v>0</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I39">
         <v>0.82</v>
@@ -2461,36 +2461,36 @@
         <v>0</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I40">
         <v>0.25</v>
@@ -2499,36 +2499,36 @@
         <v>0</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D41" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E41" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I41">
         <v>0.28999999999999998</v>
@@ -2537,36 +2537,36 @@
         <v>0</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="H42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I42">
         <v>0.19</v>
@@ -2575,36 +2575,36 @@
         <v>0</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D43" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E43" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G43">
         <v>3</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43">
         <v>0.38</v>
@@ -2613,36 +2613,36 @@
         <v>0</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L43" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D44" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F44" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G44">
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44">
         <v>0.35</v>
@@ -2651,36 +2651,36 @@
         <v>0</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L44" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D45" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E45" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G45">
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I45">
         <v>0.26500000000000001</v>
@@ -2689,36 +2689,36 @@
         <v>0</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D46" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F46" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46">
         <v>0.12</v>
@@ -2727,36 +2727,36 @@
         <v>0</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L46" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F47" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G47">
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I47">
         <v>0.43</v>
@@ -2765,36 +2765,36 @@
         <v>0</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L47" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E48" t="s">
+        <v>103</v>
+      </c>
+      <c r="F48" t="s">
         <v>104</v>
-      </c>
-      <c r="F48" t="s">
-        <v>105</v>
       </c>
       <c r="G48">
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I48">
         <v>0.87</v>
@@ -2803,36 +2803,36 @@
         <v>0</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F49" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G49">
         <v>16</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I49">
         <v>0.22</v>
@@ -2841,36 +2841,36 @@
         <v>0</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D50" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I50">
         <v>0.05</v>
@@ -2879,36 +2879,36 @@
         <v>0</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G51">
         <v>4</v>
       </c>
       <c r="H51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I51">
         <v>0.44</v>
@@ -2917,36 +2917,36 @@
         <v>0</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L51" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I52">
         <v>0.2</v>
@@ -2955,36 +2955,36 @@
         <v>0</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L52" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D53" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E53" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F53" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G53">
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I53">
         <v>2</v>
@@ -2993,36 +2993,36 @@
         <v>0</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L53" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D54" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E54" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" t="s">
         <v>118</v>
-      </c>
-      <c r="F54" t="s">
-        <v>119</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I54">
         <v>0.22500000000000001</v>
@@ -3031,36 +3031,36 @@
         <v>0</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E55" t="s">
+        <v>119</v>
+      </c>
+      <c r="F55" t="s">
         <v>120</v>
-      </c>
-      <c r="F55" t="s">
-        <v>121</v>
       </c>
       <c r="G55">
         <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I55">
         <v>0.14399999999999999</v>
@@ -3069,36 +3069,36 @@
         <v>0</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D56" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E56" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G56">
         <v>4</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I56">
         <v>0.2</v>
@@ -3107,36 +3107,36 @@
         <v>0</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L56" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F57" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I57">
         <v>0.27</v>
@@ -3145,36 +3145,36 @@
         <v>0</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L57" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E58" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F58" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G58">
         <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I58">
         <v>0.46</v>
@@ -3183,36 +3183,36 @@
         <v>0</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L58" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E59" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F59" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G59">
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I59">
         <v>0.05</v>
@@ -3221,36 +3221,36 @@
         <v>0</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E60" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G60">
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I60">
         <v>0.13</v>
@@ -3259,36 +3259,36 @@
         <v>0</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D61" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E61" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G61">
         <v>3</v>
       </c>
       <c r="H61" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I61">
         <v>0.21</v>
@@ -3297,36 +3297,36 @@
         <v>0</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L61" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F62" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G62">
         <v>7</v>
       </c>
       <c r="H62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I62">
         <v>0.16</v>
@@ -3335,36 +3335,36 @@
         <v>0</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E63" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F63" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G63">
         <v>3</v>
       </c>
       <c r="H63" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I63">
         <v>4.2999999999999997E-2</v>
@@ -3373,36 +3373,36 @@
         <v>0</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L63" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F64" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G64">
         <v>2</v>
       </c>
       <c r="H64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I64">
         <v>0.32500000000000001</v>
@@ -3411,36 +3411,36 @@
         <v>0</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D65" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E65" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F65" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G65">
         <v>3</v>
       </c>
       <c r="H65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65">
         <v>0.59</v>
@@ -3449,36 +3449,36 @@
         <v>0</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E66" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F66" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G66">
         <v>11</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66">
         <v>0.42</v>
@@ -3487,36 +3487,36 @@
         <v>0</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L66" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E67" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I67">
         <v>0.56999999999999995</v>
@@ -3525,36 +3525,36 @@
         <v>0</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L67" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E68" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F68" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I68">
         <v>0.64500000000000002</v>
@@ -3563,36 +3563,36 @@
         <v>0</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L68" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F69" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G69">
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I69">
         <v>0.22500000000000001</v>
@@ -3601,36 +3601,36 @@
         <v>121</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F70" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I70">
         <v>7.0000000000000007E-2</v>
@@ -3639,36 +3639,36 @@
         <v>144</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L70" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G71">
         <v>6</v>
       </c>
       <c r="H71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I71">
         <v>0.377</v>
@@ -3677,36 +3677,36 @@
         <v>75.83</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L71" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E72" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F72" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I72">
         <v>0.25</v>
@@ -3715,36 +3715,36 @@
         <v>499</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L72" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E73" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F73" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I73">
         <v>0.25</v>
@@ -3753,36 +3753,36 @@
         <v>499</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L73" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D74" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E74" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F74" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G74">
         <v>11</v>
       </c>
       <c r="H74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I74">
         <v>0.35</v>
@@ -3791,36 +3791,36 @@
         <v>59</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L74" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G75">
         <v>3</v>
       </c>
       <c r="H75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I75">
         <v>0.4</v>
@@ -3829,36 +3829,36 @@
         <v>84</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L75" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D76" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E76" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I76">
         <v>0.44</v>
@@ -3867,36 +3867,36 @@
         <v>84</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="L76" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F77" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G77">
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I77">
         <v>0.31</v>
@@ -3905,36 +3905,36 @@
         <v>149</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L77" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E78" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I78">
         <v>0.433</v>
@@ -3943,36 +3943,36 @@
         <v>198</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L78" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G79">
         <v>3</v>
       </c>
       <c r="H79" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I79">
         <v>10</v>
@@ -3981,36 +3981,36 @@
         <v>0</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E80" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F80" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G80">
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I80">
         <v>0.53</v>
@@ -4019,36 +4019,36 @@
         <v>227</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L80" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E81" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F81" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G81">
         <v>2</v>
       </c>
       <c r="H81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I81">
         <v>0.18</v>
@@ -4057,36 +4057,36 @@
         <v>35.200000000000003</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L81" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D82" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E82" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G82">
         <v>3</v>
       </c>
       <c r="H82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I82">
         <v>0.38300000000000001</v>
@@ -4095,36 +4095,36 @@
         <v>55</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D83" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E83" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F83" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I83">
         <v>0.13</v>
@@ -4133,36 +4133,36 @@
         <v>35</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L83" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E84" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G84">
         <v>7</v>
       </c>
       <c r="H84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I84">
         <v>0.45</v>
@@ -4171,36 +4171,36 @@
         <v>45.5</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L84" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>169</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
         <v>170</v>
       </c>
-      <c r="B85" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
         <v>171</v>
       </c>
-      <c r="D85" t="s">
-        <v>14</v>
-      </c>
-      <c r="E85" t="s">
-        <v>172</v>
-      </c>
       <c r="F85" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G85">
         <v>8352</v>
       </c>
       <c r="H85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I85">
         <v>0.18</v>
@@ -4209,36 +4209,36 @@
         <v>0</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
         <v>170</v>
       </c>
-      <c r="B86" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" t="s">
-        <v>171</v>
-      </c>
       <c r="D86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E86" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G86">
         <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I86">
         <v>0.56999999999999995</v>
@@ -4247,36 +4247,36 @@
         <v>316</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L86" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
         <v>170</v>
       </c>
-      <c r="B87" t="s">
-        <v>12</v>
-      </c>
-      <c r="C87" t="s">
-        <v>171</v>
-      </c>
       <c r="D87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E87" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F87" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G87">
         <v>27</v>
       </c>
       <c r="H87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I87">
         <v>0.33</v>
@@ -4285,36 +4285,36 @@
         <v>111</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L87" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
         <v>170</v>
       </c>
-      <c r="B88" t="s">
-        <v>12</v>
-      </c>
-      <c r="C88" t="s">
-        <v>171</v>
-      </c>
       <c r="D88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E88" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F88" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G88">
         <v>12</v>
       </c>
       <c r="H88" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I88">
         <v>0.86</v>
@@ -4323,10 +4323,10 @@
         <v>91</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="L88" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
